--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7363636363636363</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7464788732394366</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="D2">
-        <v>0.3076923076923077</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <v>7</v>
-      </c>
-      <c r="G2">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8076923076923077</v>
+        <v>0.8294573643410853</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7887323943661971</v>
+        <v>0.8028169014084507</v>
       </c>
       <c r="D2">
-        <v>0.2222222222222222</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="E2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>7</v>
